--- a/curation/draft/crf/CRF_QRS_EQ5D-5L.xlsx
+++ b/curation/draft/crf/CRF_QRS_EQ5D-5L.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\_github\cdisc-org\COSMoS\curation\draft\crf\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A54A2454-97B7-4922-B429-7B5B3641D184}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D27AE61-E46F-4BC2-8DCD-1E0B3958B39A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -19,7 +19,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Collection Specializations- v1'!$A$1:$AI$16</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" concurrentCalc="0"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -162,7 +162,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="659" uniqueCount="168">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="655" uniqueCount="169">
   <si>
     <t>package_date</t>
   </si>
@@ -666,6 +666,9 @@
   </si>
   <si>
     <t>float</t>
+  </si>
+  <si>
+    <t>C82534</t>
   </si>
 </sst>
 </file>
@@ -1251,9 +1254,7 @@
       <c r="B2" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="C2" s="4" t="s">
-        <v>55</v>
-      </c>
+      <c r="C2" s="4"/>
       <c r="D2" s="4" t="s">
         <v>36</v>
       </c>
@@ -1335,9 +1336,7 @@
       <c r="B3" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="C3" s="4" t="s">
-        <v>55</v>
-      </c>
+      <c r="C3" s="4"/>
       <c r="D3" s="4" t="s">
         <v>36</v>
       </c>
@@ -1421,9 +1420,7 @@
       <c r="B4" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="C4" s="4" t="s">
-        <v>55</v>
-      </c>
+      <c r="C4" s="4"/>
       <c r="D4" s="4" t="s">
         <v>36</v>
       </c>
@@ -1497,9 +1494,7 @@
       <c r="B5" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="C5" s="4" t="s">
-        <v>55</v>
-      </c>
+      <c r="C5" s="4"/>
       <c r="D5" s="4" t="s">
         <v>36</v>
       </c>
@@ -1526,7 +1521,7 @@
         <v>158</v>
       </c>
       <c r="O5" s="5" t="s">
-        <v>73</v>
+        <v>168</v>
       </c>
       <c r="P5" s="6"/>
       <c r="Q5" s="6" t="s">
@@ -2460,30 +2455,30 @@
     <hyperlink ref="B4" r:id="rId8" xr:uid="{80C64E24-3665-4403-A995-865677F77EE7}"/>
     <hyperlink ref="O4" r:id="rId9" xr:uid="{BA91C02B-C49E-4095-A07C-396249C526E3}"/>
     <hyperlink ref="B5" r:id="rId10" xr:uid="{0CA58E18-B50C-4771-AC4E-EA34C312208F}"/>
-    <hyperlink ref="O5" r:id="rId11" xr:uid="{AD8A051B-CA74-4BEF-B3F5-F9F869742A1C}"/>
-    <hyperlink ref="B6" r:id="rId12" xr:uid="{365D1F42-0F1E-483C-8FA3-1ECA4EBEE205}"/>
-    <hyperlink ref="O6" r:id="rId13" xr:uid="{50D79DF0-430E-41F0-BAD9-531B1F1D0C54}"/>
-    <hyperlink ref="B7" r:id="rId14" xr:uid="{7B794814-A34A-4C95-A8F0-22FAE065CF77}"/>
-    <hyperlink ref="O7" r:id="rId15" xr:uid="{022648F0-6EE0-4B42-8AE7-DF382A5295B2}"/>
-    <hyperlink ref="B8" r:id="rId16" xr:uid="{2E9D35D9-2F92-46FC-814B-6F65CF01D6B8}"/>
-    <hyperlink ref="O8" r:id="rId17" xr:uid="{8741FDAB-3FA0-4842-8ACD-6302AF2DB1CE}"/>
-    <hyperlink ref="B9" r:id="rId18" xr:uid="{9B7F1052-3A20-4E1A-861F-03C50F73607F}"/>
-    <hyperlink ref="O9" r:id="rId19" xr:uid="{96FC4501-E245-4D12-A3D8-DEFEB0D08872}"/>
-    <hyperlink ref="B10" r:id="rId20" xr:uid="{F88EE80B-682E-49FB-8572-8CD5714A7B5C}"/>
-    <hyperlink ref="O10" r:id="rId21" xr:uid="{8DF8B8F3-8ACE-4857-81E6-1D9E03166BC3}"/>
-    <hyperlink ref="B11" r:id="rId22" xr:uid="{6FF786E1-EDA2-4647-A685-CDA8D83FBEAB}"/>
-    <hyperlink ref="O11" r:id="rId23" xr:uid="{C1767D78-2EB0-4B41-A72D-5EA8809BCACF}"/>
-    <hyperlink ref="B12" r:id="rId24" xr:uid="{F793B396-27FD-4ABF-A3D7-A1E63F107CD3}"/>
-    <hyperlink ref="O12" r:id="rId25" xr:uid="{1B06A19E-6DA2-4EE4-8EAE-CF13E746E833}"/>
-    <hyperlink ref="AG12" r:id="rId26" xr:uid="{8F34D6F5-1598-4E4A-B96C-FDD1E24D7972}"/>
-    <hyperlink ref="B13" r:id="rId27" xr:uid="{2BFF1B89-DD48-48E2-A9FF-7A780C3BD170}"/>
-    <hyperlink ref="O13" r:id="rId28" xr:uid="{9B2714F1-55F3-4203-8B8F-55E918C1C4F5}"/>
-    <hyperlink ref="B14" r:id="rId29" xr:uid="{357E189F-5E1C-433E-9328-75CE2E3E8FA6}"/>
-    <hyperlink ref="O14" r:id="rId30" xr:uid="{2383C550-BA08-457F-8BC5-5DC952B5E637}"/>
-    <hyperlink ref="B15" r:id="rId31" xr:uid="{B6F6493A-26A0-427C-9CAF-7169E699402B}"/>
-    <hyperlink ref="O15" r:id="rId32" xr:uid="{7DCC2FB3-F2FC-4923-A26C-4F99A2D1BE0E}"/>
-    <hyperlink ref="B16" r:id="rId33" xr:uid="{3B88B096-C5F0-430F-9866-3D1E8160487B}"/>
-    <hyperlink ref="O16" r:id="rId34" xr:uid="{09392FEF-D146-4514-B702-D2EB2ACB5848}"/>
+    <hyperlink ref="B6" r:id="rId11" xr:uid="{365D1F42-0F1E-483C-8FA3-1ECA4EBEE205}"/>
+    <hyperlink ref="O6" r:id="rId12" xr:uid="{50D79DF0-430E-41F0-BAD9-531B1F1D0C54}"/>
+    <hyperlink ref="B7" r:id="rId13" xr:uid="{7B794814-A34A-4C95-A8F0-22FAE065CF77}"/>
+    <hyperlink ref="O7" r:id="rId14" xr:uid="{022648F0-6EE0-4B42-8AE7-DF382A5295B2}"/>
+    <hyperlink ref="B8" r:id="rId15" xr:uid="{2E9D35D9-2F92-46FC-814B-6F65CF01D6B8}"/>
+    <hyperlink ref="O8" r:id="rId16" xr:uid="{8741FDAB-3FA0-4842-8ACD-6302AF2DB1CE}"/>
+    <hyperlink ref="B9" r:id="rId17" xr:uid="{9B7F1052-3A20-4E1A-861F-03C50F73607F}"/>
+    <hyperlink ref="O9" r:id="rId18" xr:uid="{96FC4501-E245-4D12-A3D8-DEFEB0D08872}"/>
+    <hyperlink ref="B10" r:id="rId19" xr:uid="{F88EE80B-682E-49FB-8572-8CD5714A7B5C}"/>
+    <hyperlink ref="O10" r:id="rId20" xr:uid="{8DF8B8F3-8ACE-4857-81E6-1D9E03166BC3}"/>
+    <hyperlink ref="B11" r:id="rId21" xr:uid="{6FF786E1-EDA2-4647-A685-CDA8D83FBEAB}"/>
+    <hyperlink ref="O11" r:id="rId22" xr:uid="{C1767D78-2EB0-4B41-A72D-5EA8809BCACF}"/>
+    <hyperlink ref="B12" r:id="rId23" xr:uid="{F793B396-27FD-4ABF-A3D7-A1E63F107CD3}"/>
+    <hyperlink ref="O12" r:id="rId24" xr:uid="{1B06A19E-6DA2-4EE4-8EAE-CF13E746E833}"/>
+    <hyperlink ref="AG12" r:id="rId25" xr:uid="{8F34D6F5-1598-4E4A-B96C-FDD1E24D7972}"/>
+    <hyperlink ref="B13" r:id="rId26" xr:uid="{2BFF1B89-DD48-48E2-A9FF-7A780C3BD170}"/>
+    <hyperlink ref="O13" r:id="rId27" xr:uid="{9B2714F1-55F3-4203-8B8F-55E918C1C4F5}"/>
+    <hyperlink ref="B14" r:id="rId28" xr:uid="{357E189F-5E1C-433E-9328-75CE2E3E8FA6}"/>
+    <hyperlink ref="O14" r:id="rId29" xr:uid="{2383C550-BA08-457F-8BC5-5DC952B5E637}"/>
+    <hyperlink ref="B15" r:id="rId30" xr:uid="{B6F6493A-26A0-427C-9CAF-7169E699402B}"/>
+    <hyperlink ref="O15" r:id="rId31" xr:uid="{7DCC2FB3-F2FC-4923-A26C-4F99A2D1BE0E}"/>
+    <hyperlink ref="B16" r:id="rId32" xr:uid="{3B88B096-C5F0-430F-9866-3D1E8160487B}"/>
+    <hyperlink ref="O16" r:id="rId33" xr:uid="{09392FEF-D146-4514-B702-D2EB2ACB5848}"/>
+    <hyperlink ref="O5" r:id="rId34" xr:uid="{9957C926-6B10-4D2D-B30F-32125D49525A}"/>
   </hyperlinks>
   <pageMargins left="0.05" right="0.05" top="0.5" bottom="0.5" header="0" footer="0"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
